--- a/DataframeAval2.xlsx
+++ b/DataframeAval2.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Plan1!$A$1:$C$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Plan1!$A$1:$C$41</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="5">
   <si>
     <t>Companhia</t>
   </si>
@@ -30,7 +30,13 @@
     <t>Grupo</t>
   </si>
   <si>
-    <t>DiasAtraso</t>
+    <t>Tradicional</t>
+  </si>
+  <si>
+    <t>Novo Mercado</t>
+  </si>
+  <si>
+    <t>Payout</t>
   </si>
 </sst>
 </file>
@@ -62,7 +68,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -70,35 +76,23 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -448,521 +442,467 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.19921875" customWidth="1"/>
-    <col min="3" max="3" width="11.69921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="1">
-        <v>0</v>
+      <c r="B2" s="4" t="s">
+        <v>2</v>
       </c>
       <c r="C2" s="1">
-        <v>7</v>
+        <v>0.38400000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="1">
-        <v>0</v>
+      <c r="B3" s="4" t="s">
+        <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>5</v>
+        <v>0.41199999999999998</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="1">
-        <v>0</v>
+      <c r="B4" s="4" t="s">
+        <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>7</v>
+        <v>0.437</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="1">
-        <v>0</v>
+      <c r="B5" s="4" t="s">
+        <v>2</v>
       </c>
       <c r="C5" s="1">
-        <v>8</v>
+        <v>0.45100000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="1">
-        <v>0</v>
+      <c r="B6" s="4" t="s">
+        <v>2</v>
       </c>
       <c r="C6" s="1">
-        <v>9</v>
+        <v>0.46300000000000002</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="1">
-        <v>0</v>
+      <c r="B7" s="4" t="s">
+        <v>2</v>
       </c>
       <c r="C7" s="1">
-        <v>4</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="1">
-        <v>0</v>
+      <c r="B8" s="4" t="s">
+        <v>2</v>
       </c>
       <c r="C8" s="1">
-        <v>5</v>
+        <v>0.47799999999999998</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="1">
-        <v>0</v>
+      <c r="B9" s="4" t="s">
+        <v>2</v>
       </c>
       <c r="C9" s="1">
-        <v>6</v>
+        <v>0.48499999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="1">
-        <v>0</v>
+      <c r="B10" s="4" t="s">
+        <v>2</v>
       </c>
       <c r="C10" s="1">
-        <v>7</v>
+        <v>0.49199999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="1">
-        <v>0</v>
+      <c r="B11" s="4" t="s">
+        <v>2</v>
       </c>
       <c r="C11" s="1">
-        <v>8</v>
+        <v>0.498</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="1">
-        <v>0</v>
+      <c r="B12" s="4" t="s">
+        <v>2</v>
       </c>
       <c r="C12" s="1">
-        <v>7</v>
+        <v>0.501</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="1">
-        <v>0</v>
+      <c r="B13" s="4" t="s">
+        <v>2</v>
       </c>
       <c r="C13" s="1">
-        <v>8</v>
+        <v>0.50700000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="1">
-        <v>0</v>
+      <c r="B14" s="4" t="s">
+        <v>2</v>
       </c>
       <c r="C14" s="1">
-        <v>9</v>
+        <v>0.51300000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="1">
-        <v>0</v>
+      <c r="B15" s="4" t="s">
+        <v>2</v>
       </c>
       <c r="C15" s="1">
-        <v>7</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="1">
-        <v>0</v>
+      <c r="B16" s="4" t="s">
+        <v>2</v>
       </c>
       <c r="C16" s="1">
-        <v>8</v>
+        <v>0.52800000000000002</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="B17" s="1">
-        <v>0</v>
+      <c r="B17" s="4" t="s">
+        <v>2</v>
       </c>
       <c r="C17" s="1">
-        <v>6</v>
+        <v>0.53400000000000003</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="B18" s="1">
-        <v>0</v>
+      <c r="B18" s="4" t="s">
+        <v>2</v>
       </c>
       <c r="C18" s="1">
-        <v>10</v>
+        <v>0.54100000000000004</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="B19" s="1">
-        <v>0</v>
+      <c r="B19" s="4" t="s">
+        <v>2</v>
       </c>
       <c r="C19" s="1">
-        <v>8</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="B20" s="1">
-        <v>0</v>
+      <c r="B20" s="4" t="s">
+        <v>2</v>
       </c>
       <c r="C20" s="1">
-        <v>7</v>
+        <v>0.56200000000000006</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="B21" s="1">
-        <v>0</v>
+      <c r="B21" s="4" t="s">
+        <v>2</v>
       </c>
       <c r="C21" s="1">
-        <v>5</v>
+        <v>0.57599999999999996</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="B22" s="1">
-        <v>0</v>
+      <c r="B22" s="4" t="s">
+        <v>2</v>
       </c>
       <c r="C22" s="1">
-        <v>3</v>
+        <v>0.59299999999999997</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>22</v>
       </c>
-      <c r="B23" s="1">
-        <v>0</v>
+      <c r="B23" s="4" t="s">
+        <v>2</v>
       </c>
       <c r="C23" s="1">
-        <v>6</v>
+        <v>0.44800000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>23</v>
       </c>
-      <c r="B24" s="1">
-        <v>0</v>
+      <c r="B24" s="4" t="s">
+        <v>2</v>
       </c>
       <c r="C24" s="1">
-        <v>7</v>
+        <v>0.46899999999999997</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>24</v>
       </c>
-      <c r="B25" s="1">
-        <v>0</v>
+      <c r="B25" s="4" t="s">
+        <v>2</v>
       </c>
       <c r="C25" s="1">
-        <v>5</v>
+        <v>0.51800000000000002</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>25</v>
       </c>
-      <c r="B26" s="1">
-        <v>0</v>
+      <c r="B26" s="4" t="s">
+        <v>2</v>
       </c>
       <c r="C26" s="1">
-        <v>4</v>
+        <v>0.53700000000000003</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>26</v>
       </c>
-      <c r="B27" s="3">
-        <v>1</v>
+      <c r="B27" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C27" s="1">
-        <v>6</v>
+        <v>0.40500000000000003</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>27</v>
       </c>
-      <c r="B28" s="3">
-        <v>1</v>
+      <c r="B28" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C28" s="1">
-        <v>4</v>
+        <v>0.42299999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>28</v>
       </c>
-      <c r="B29" s="3">
-        <v>1</v>
+      <c r="B29" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C29" s="1">
-        <v>5</v>
+        <v>0.439</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>29</v>
       </c>
-      <c r="B30" s="3">
-        <v>1</v>
+      <c r="B30" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C30" s="1">
-        <v>6</v>
+        <v>0.45600000000000002</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>30</v>
       </c>
-      <c r="B31" s="3">
-        <v>1</v>
+      <c r="B31" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C31" s="1">
-        <v>3</v>
+        <v>0.46800000000000003</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>31</v>
       </c>
-      <c r="B32" s="3">
-        <v>1</v>
+      <c r="B32" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C32" s="1">
-        <v>7</v>
+        <v>0.47499999999999998</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>32</v>
       </c>
-      <c r="B33" s="3">
-        <v>1</v>
+      <c r="B33" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C33" s="1">
-        <v>8</v>
+        <v>0.48899999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>33</v>
       </c>
-      <c r="B34" s="3">
-        <v>1</v>
+      <c r="B34" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C34" s="1">
-        <v>9</v>
+        <v>0.495</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>34</v>
       </c>
-      <c r="B35" s="3">
-        <v>1</v>
+      <c r="B35" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C35" s="1">
-        <v>3</v>
+        <v>0.504</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>35</v>
       </c>
-      <c r="B36" s="3">
-        <v>1</v>
+      <c r="B36" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C36" s="1">
-        <v>5</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>36</v>
       </c>
-      <c r="B37" s="3">
-        <v>1</v>
+      <c r="B37" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C37" s="1">
-        <v>4</v>
+        <v>0.51900000000000002</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>37</v>
       </c>
-      <c r="B38" s="3">
-        <v>1</v>
+      <c r="B38" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C38" s="1">
-        <v>5</v>
+        <v>0.52600000000000002</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>38</v>
       </c>
-      <c r="B39" s="3">
-        <v>1</v>
+      <c r="B39" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C39" s="1">
-        <v>7</v>
+        <v>0.53200000000000003</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>39</v>
       </c>
-      <c r="B40" s="3">
-        <v>1</v>
+      <c r="B40" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C40" s="1">
-        <v>6</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>40</v>
       </c>
-      <c r="B41" s="3">
-        <v>1</v>
+      <c r="B41" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C41" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="1">
-        <v>41</v>
-      </c>
-      <c r="B42" s="3">
-        <v>1</v>
-      </c>
-      <c r="C42" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="1">
-        <v>42</v>
-      </c>
-      <c r="B43" s="3">
-        <v>1</v>
-      </c>
-      <c r="C43" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="1">
-        <v>43</v>
-      </c>
-      <c r="B44" s="3">
-        <v>1</v>
-      </c>
-      <c r="C44" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="1">
-        <v>44</v>
-      </c>
-      <c r="B45" s="3">
-        <v>1</v>
-      </c>
-      <c r="C45" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="1">
-        <v>45</v>
-      </c>
-      <c r="B46" s="3">
-        <v>1</v>
-      </c>
-      <c r="C46" s="1">
-        <v>6</v>
+        <v>0.55400000000000005</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C46"/>
+  <autoFilter ref="A1:C41"/>
   <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0.3" footer="0.3"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>

--- a/DataframeAval2.xlsx
+++ b/DataframeAval2.xlsx
@@ -14,15 +14,12 @@
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Plan1!$A$1:$C$46</definedName>
-  </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="5">
   <si>
     <t>Companhia</t>
   </si>
@@ -30,7 +27,13 @@
     <t>Grupo</t>
   </si>
   <si>
-    <t>DiasAtraso</t>
+    <t>Payout</t>
+  </si>
+  <si>
+    <t>Tradicional</t>
+  </si>
+  <si>
+    <t>Novo Mercado</t>
   </si>
 </sst>
 </file>
@@ -62,7 +65,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -70,35 +73,23 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -451,15 +442,14 @@
   <dimension ref="A1:C46"/>
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.19921875" customWidth="1"/>
-    <col min="3" max="3" width="11.69921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.19921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -470,499 +460,498 @@
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="1">
-        <v>0</v>
+      <c r="B2" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C2" s="1">
-        <v>7</v>
+        <v>0.38400000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="1">
-        <v>0</v>
+      <c r="B3" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C3" s="1">
-        <v>5</v>
+        <v>0.41199999999999998</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="1">
-        <v>0</v>
+      <c r="B4" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C4" s="1">
-        <v>7</v>
+        <v>0.437</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="1">
-        <v>0</v>
+      <c r="B5" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C5" s="1">
-        <v>8</v>
+        <v>0.45100000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="1">
-        <v>0</v>
+      <c r="B6" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C6" s="1">
-        <v>9</v>
+        <v>0.46300000000000002</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="1">
-        <v>0</v>
+      <c r="B7" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C7" s="1">
-        <v>4</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="1">
-        <v>0</v>
+      <c r="B8" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C8" s="1">
-        <v>5</v>
+        <v>0.47799999999999998</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="1">
-        <v>0</v>
+      <c r="B9" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C9" s="1">
-        <v>6</v>
+        <v>0.48499999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="1">
-        <v>0</v>
+      <c r="B10" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C10" s="1">
-        <v>7</v>
+        <v>0.49199999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="1">
-        <v>0</v>
+      <c r="B11" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C11" s="1">
-        <v>8</v>
+        <v>0.498</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="1">
-        <v>0</v>
+      <c r="B12" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C12" s="1">
-        <v>7</v>
+        <v>0.501</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="1">
-        <v>0</v>
+      <c r="B13" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C13" s="1">
-        <v>8</v>
+        <v>0.50700000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="1">
-        <v>0</v>
+      <c r="B14" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C14" s="1">
-        <v>9</v>
+        <v>0.51300000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="1">
-        <v>0</v>
+      <c r="B15" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C15" s="1">
-        <v>7</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="1">
-        <v>0</v>
+      <c r="B16" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C16" s="1">
-        <v>8</v>
+        <v>0.52800000000000002</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="B17" s="1">
-        <v>0</v>
+      <c r="B17" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C17" s="1">
-        <v>6</v>
+        <v>0.53400000000000003</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="B18" s="1">
-        <v>0</v>
+      <c r="B18" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C18" s="1">
-        <v>10</v>
+        <v>0.54100000000000004</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="B19" s="1">
-        <v>0</v>
+      <c r="B19" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C19" s="1">
-        <v>8</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="B20" s="1">
-        <v>0</v>
+      <c r="B20" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C20" s="1">
-        <v>7</v>
+        <v>0.56200000000000006</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="B21" s="1">
-        <v>0</v>
+      <c r="B21" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C21" s="1">
-        <v>5</v>
+        <v>0.57599999999999996</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="B22" s="1">
-        <v>0</v>
+      <c r="B22" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C22" s="1">
-        <v>3</v>
+        <v>0.59299999999999997</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>22</v>
       </c>
-      <c r="B23" s="1">
-        <v>0</v>
+      <c r="B23" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C23" s="1">
-        <v>6</v>
+        <v>0.44800000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>23</v>
       </c>
-      <c r="B24" s="1">
-        <v>0</v>
+      <c r="B24" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C24" s="1">
-        <v>7</v>
+        <v>0.46899999999999997</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>24</v>
       </c>
-      <c r="B25" s="1">
-        <v>0</v>
+      <c r="B25" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C25" s="1">
-        <v>5</v>
+        <v>0.51800000000000002</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>25</v>
       </c>
-      <c r="B26" s="1">
-        <v>0</v>
+      <c r="B26" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C26" s="1">
-        <v>4</v>
+        <v>0.53700000000000003</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>26</v>
       </c>
-      <c r="B27" s="3">
-        <v>1</v>
+      <c r="B27" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="C27" s="1">
-        <v>6</v>
+        <v>0.40500000000000003</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>27</v>
       </c>
-      <c r="B28" s="3">
-        <v>1</v>
+      <c r="B28" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="C28" s="1">
-        <v>4</v>
+        <v>0.42299999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>28</v>
       </c>
-      <c r="B29" s="3">
-        <v>1</v>
+      <c r="B29" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="C29" s="1">
-        <v>5</v>
+        <v>0.439</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>29</v>
       </c>
-      <c r="B30" s="3">
-        <v>1</v>
+      <c r="B30" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="C30" s="1">
-        <v>6</v>
+        <v>0.45600000000000002</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>30</v>
       </c>
-      <c r="B31" s="3">
-        <v>1</v>
+      <c r="B31" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="C31" s="1">
-        <v>3</v>
+        <v>0.46800000000000003</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>31</v>
       </c>
-      <c r="B32" s="3">
-        <v>1</v>
+      <c r="B32" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="C32" s="1">
-        <v>7</v>
+        <v>0.47499999999999998</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>32</v>
       </c>
-      <c r="B33" s="3">
-        <v>1</v>
+      <c r="B33" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="C33" s="1">
-        <v>8</v>
+        <v>0.48899999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>33</v>
       </c>
-      <c r="B34" s="3">
-        <v>1</v>
+      <c r="B34" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="C34" s="1">
-        <v>9</v>
+        <v>0.495</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>34</v>
       </c>
-      <c r="B35" s="3">
-        <v>1</v>
+      <c r="B35" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="C35" s="1">
-        <v>3</v>
+        <v>0.504</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>35</v>
       </c>
-      <c r="B36" s="3">
-        <v>1</v>
+      <c r="B36" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="C36" s="1">
-        <v>5</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>36</v>
       </c>
-      <c r="B37" s="3">
-        <v>1</v>
+      <c r="B37" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="C37" s="1">
-        <v>4</v>
+        <v>0.51900000000000002</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>37</v>
       </c>
-      <c r="B38" s="3">
-        <v>1</v>
+      <c r="B38" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="C38" s="1">
-        <v>5</v>
+        <v>0.52600000000000002</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>38</v>
       </c>
-      <c r="B39" s="3">
-        <v>1</v>
+      <c r="B39" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="C39" s="1">
-        <v>7</v>
+        <v>0.53200000000000003</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>39</v>
       </c>
-      <c r="B40" s="3">
-        <v>1</v>
+      <c r="B40" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="C40" s="1">
-        <v>6</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>40</v>
       </c>
-      <c r="B41" s="3">
-        <v>1</v>
+      <c r="B41" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="C41" s="1">
-        <v>5</v>
+        <v>0.55400000000000005</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>41</v>
       </c>
-      <c r="B42" s="3">
-        <v>1</v>
+      <c r="B42" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="C42" s="1">
-        <v>3</v>
+        <v>0.56799999999999995</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>42</v>
       </c>
-      <c r="B43" s="3">
-        <v>1</v>
+      <c r="B43" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="C43" s="1">
-        <v>4</v>
+        <v>0.58099999999999996</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>43</v>
       </c>
-      <c r="B44" s="3">
-        <v>1</v>
+      <c r="B44" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="C44" s="1">
-        <v>5</v>
+        <v>0.48099999999999998</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>44</v>
       </c>
-      <c r="B45" s="3">
-        <v>1</v>
+      <c r="B45" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="C45" s="1">
-        <v>3</v>
+        <v>0.50900000000000001</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>45</v>
       </c>
-      <c r="B46" s="3">
-        <v>1</v>
+      <c r="B46" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="C46" s="1">
-        <v>6</v>
+        <v>0.53500000000000003</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C46"/>
   <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0.3" footer="0.3"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
